--- a/output/pdf_financials_xlsx/QSE.xlsx
+++ b/output/pdf_financials_xlsx/QSE.xlsx
@@ -726,7 +726,7 @@
         <v>-0.369065</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-11.429416</v>
@@ -818,7 +818,7 @@
         <v>-0.369065</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-11.429416</v>
@@ -875,7 +875,7 @@
         <v>-0.369065</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-11.429416</v>
@@ -975,7 +975,7 @@
         <v>-0.369065</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-11.429416</v>
@@ -1013,7 +1013,7 @@
         <v>-0.369065</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-11.429416</v>
@@ -1059,7 +1059,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -2235,16 +2235,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.17241</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.226658</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.683067</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.279324</v>
       </c>
     </row>
     <row r="93">
@@ -3624,7 +3624,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4040,7 +4044,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -4414,7 +4422,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.17241</v>
       </c>
@@ -8211,10 +8223,10 @@
         </is>
       </c>
       <c r="F143" s="5" t="n">
-        <v>3.205374</v>
+        <v>-3.205374</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>11.429416</v>
+        <v>-11.429416</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/QSE.xlsx
+++ b/output/pdf_financials_xlsx/QSE.xlsx
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.03097</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.047039</v>
       </c>
     </row>
     <row r="13">
@@ -978,10 +978,10 @@
         <v>-3.205374</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.429416</v>
+        <v>-11.398446</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.712717</v>
+        <v>-3.665678</v>
       </c>
     </row>
     <row r="28">
@@ -1016,10 +1016,10 @@
         <v>-3.205374</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.429416</v>
+        <v>-11.398446</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.712717</v>
+        <v>-3.665678</v>
       </c>
     </row>
     <row r="30">
@@ -1109,7 +1109,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.193995</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.050572</v>
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.193995</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.050572</v>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.195633</v>
+        <v>1.001638</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.054767</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" s="5" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">

--- a/output/pdf_financials_xlsx/QSE.xlsx
+++ b/output/pdf_financials_xlsx/QSE.xlsx
@@ -552,16 +552,16 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.06533799999999999</v>
+        <v>0.06689000000000001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.145546</v>
+        <v>0.154663</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.143931</v>
+        <v>0.198496</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.195902</v>
+        <v>0.351654</v>
       </c>
     </row>
     <row r="8">
@@ -729,7 +729,7 @@
         <v>-3.205374</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-11.429416</v>
+        <v>-11.419361</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-3.712717</v>
@@ -748,7 +748,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.010055</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -978,7 +978,7 @@
         <v>-3.205374</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.398446</v>
+        <v>-11.388391</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.665678</v>
@@ -1016,7 +1016,7 @@
         <v>-3.205374</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.398446</v>
+        <v>-11.388391</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.665678</v>
@@ -1062,7 +1062,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.08805221237860858</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -5354,7 +5354,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>1.430799</v>
       </c>
@@ -7018,7 +7022,11 @@
           <t>Office expenses 9</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -7494,7 +7502,11 @@
           <t>Income tax recovery</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -7832,7 +7844,11 @@
           <t>Office expenses 7</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -8180,7 +8196,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -8540,7 +8560,11 @@
           <t>Office expenses 8</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>0.001552</v>
       </c>
